--- a/WebDataAgro/Templates/AltaMasivaMATBA.xlsx
+++ b/WebDataAgro/Templates/AltaMasivaMATBA.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20390"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bmelgarejo\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dataagro\DataAgro-branch-dev\WebDataAgro\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E80D48DD-DC25-4764-AB58-85CC55317B6A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7020"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AltaMasiva" sheetId="1" r:id="rId1"/>
@@ -20,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="117">
   <si>
     <t>Contrato corredor</t>
   </si>
@@ -98,9 +99,6 @@
   </si>
   <si>
     <t xml:space="preserve">Sust a conv. </t>
-  </si>
-  <si>
-    <t>Tipo Boleto</t>
   </si>
   <si>
     <t xml:space="preserve">Observaciones </t>
@@ -379,7 +377,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -833,8 +831,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AJ77"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AH77"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.85546875" customWidth="1" collapsed="1"/>
@@ -863,44 +861,42 @@
     <col min="25" max="25" width="13.42578125" style="16" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="18.28515625" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="14.85546875" customWidth="1"/>
-    <col min="28" max="28" width="19" customWidth="1"/>
-    <col min="29" max="29" width="13.28515625" customWidth="1"/>
-    <col min="30" max="30" width="12.7109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="11" customWidth="1"/>
-    <col min="32" max="32" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="19.42578125" customWidth="1"/>
-    <col min="34" max="34" width="19.42578125" style="16" customWidth="1"/>
-    <col min="35" max="35" width="12.85546875" style="16" customWidth="1"/>
-    <col min="36" max="36" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="12.7109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="12.28515625" style="11" customWidth="1"/>
+    <col min="30" max="30" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="19.42578125" customWidth="1"/>
+    <col min="32" max="32" width="19.42578125" style="16" customWidth="1"/>
+    <col min="33" max="33" width="12.85546875" style="16" customWidth="1"/>
+    <col min="34" max="34" width="14.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:34" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D1" s="9" t="s">
         <v>50</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>51</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="F1" s="18" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>3</v>
       </c>
       <c r="H1" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>7</v>
@@ -933,58 +929,52 @@
         <v>12</v>
       </c>
       <c r="T1" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="U1" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="U1" s="17" t="s">
+      <c r="V1" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="V1" s="5" t="s">
-        <v>57</v>
-      </c>
       <c r="W1" s="13" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="X1" s="13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Y1" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z1" s="5" t="s">
         <v>74</v>
-      </c>
-      <c r="Z1" s="5" t="s">
-        <v>75</v>
       </c>
       <c r="AA1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AB1" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC1" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="AD1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE1" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="AF1" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="AG1" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="AH1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="AC1" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AD1" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="AE1" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="AF1" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="AG1" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="AH1" s="18" t="s">
-        <v>117</v>
-      </c>
-      <c r="AI1" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="AJ1" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="14"/>
@@ -1003,54 +993,52 @@
       <c r="X2" s="14"/>
       <c r="Z2" s="14"/>
       <c r="AA2" s="14"/>
-      <c r="AB2" s="14"/>
-      <c r="AC2" s="14"/>
-      <c r="AD2" s="1"/>
-      <c r="AE2" s="1"/>
-      <c r="AF2" s="14"/>
-      <c r="AG2" s="14"/>
-      <c r="AH2" s="20"/>
-    </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AB2" s="1"/>
+      <c r="AC2" s="1"/>
+      <c r="AD2" s="14"/>
+      <c r="AE2" s="14"/>
+      <c r="AF2" s="20"/>
+    </row>
+    <row r="3" spans="1:34" x14ac:dyDescent="0.25">
       <c r="M3" s="11"/>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:34" x14ac:dyDescent="0.25">
       <c r="M4" s="11"/>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.25">
       <c r="M5" s="11"/>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.25">
       <c r="M6" s="11"/>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.25">
       <c r="M7" s="11"/>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.25">
       <c r="M8" s="11"/>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.25">
       <c r="M9" s="11"/>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.25">
       <c r="M10" s="11"/>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.25">
       <c r="M11" s="11"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:34" x14ac:dyDescent="0.25">
       <c r="M12" s="11"/>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.25">
       <c r="M13" s="11"/>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:34" x14ac:dyDescent="0.25">
       <c r="M14" s="11"/>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.25">
       <c r="M15" s="11"/>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.25">
       <c r="M16" s="11"/>
     </row>
     <row r="17" spans="13:13" x14ac:dyDescent="0.25">
@@ -1242,107 +1230,107 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="17">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Clasificacion" error="El valor no es valido">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Clasificacion" error="El valor no es valido" xr:uid="{00000000-0002-0000-0000-000000000000}">
           <x14:formula1>
             <xm:f>Data!$B$2:$B$4</xm:f>
           </x14:formula1>
           <xm:sqref>N78:N1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Plan Canje" error="El valor no es valido">
+        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Plan Canje" error="El valor no es valido" xr:uid="{00000000-0002-0000-0000-000001000000}">
           <x14:formula1>
             <xm:f>Data!$C$2</xm:f>
           </x14:formula1>
           <xm:sqref>R78:R247 F78:F1048576 H78:H1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000002000000}">
           <x14:formula1>
             <xm:f>Data!$E$2:$E$6</xm:f>
           </x14:formula1>
-          <xm:sqref>S78:S247 AB2:AB1048576</xm:sqref>
+          <xm:sqref>S78:S247</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000003000000}">
           <x14:formula1>
             <xm:f>Data!$F$2:$F$7</xm:f>
           </x14:formula1>
-          <xm:sqref>T78:T247 AC2:AC1048576</xm:sqref>
+          <xm:sqref>T78:T247</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000004000000}">
           <x14:formula1>
             <xm:f>Data!$A$2:$A$5</xm:f>
           </x14:formula1>
           <xm:sqref>E3:E1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Grano" error="El valor no es valido">
+        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Grano" error="El valor no es valido" xr:uid="{00000000-0002-0000-0000-000005000000}">
           <x14:formula1>
             <xm:f>Data!$J$2</xm:f>
           </x14:formula1>
           <xm:sqref>C2:C1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000006000000}">
           <x14:formula1>
             <xm:f>Data!$K$2:$K$3</xm:f>
           </x14:formula1>
           <xm:sqref>D2:D1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000007000000}">
           <x14:formula1>
             <xm:f>Data!$L$2:$L$3</xm:f>
           </x14:formula1>
           <xm:sqref>I2:I1048576 V2:V1048576 Z2:Z1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Consignatario" error="El valor no es valido">
+        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Consignatario" error="El valor no es valido" xr:uid="{00000000-0002-0000-0000-000008000000}">
           <x14:formula1>
             <xm:f>Data!$B$2:$B$4</xm:f>
           </x14:formula1>
           <xm:sqref>J2:J1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Destino" error="El valor no es valido">
+        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Destino" error="El valor no es valido" xr:uid="{00000000-0002-0000-0000-000009000000}">
           <x14:formula1>
             <xm:f>Data!$C$2</xm:f>
           </x14:formula1>
           <xm:sqref>O2:O1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00000A000000}">
           <x14:formula1>
             <xm:f>Data!$C$2</xm:f>
           </x14:formula1>
           <xm:sqref>P2:P1048576 AA2:AA1048576 X2:X83</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00000B000000}">
           <x14:formula1>
             <xm:f>Data!$D$2:$D$10</xm:f>
           </x14:formula1>
           <xm:sqref>Q2:Q1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00000C000000}">
           <x14:formula1>
             <xm:f>Data!$M$2</xm:f>
           </x14:formula1>
           <xm:sqref>W3:W1048576 X84:X1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00000D000000}">
           <x14:formula1>
             <xm:f>Data!$H$2:$H$4</xm:f>
           </x14:formula1>
-          <xm:sqref>AF2:AF1048576</xm:sqref>
+          <xm:sqref>AD2:AD1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00000E000000}">
           <x14:formula1>
             <xm:f>Data!$M$2:$M$35</xm:f>
           </x14:formula1>
           <xm:sqref>W2</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-00000F000000}">
           <x14:formula1>
             <xm:f>Data!$A$2:$A$6</xm:f>
           </x14:formula1>
           <xm:sqref>E2</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000010000000}">
           <x14:formula1>
             <xm:f>Data!$N$2:$N$5</xm:f>
           </x14:formula1>
-          <xm:sqref>AG2:AG1048576</xm:sqref>
+          <xm:sqref>AE2:AE1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1351,7 +1339,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:N35"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1380,39 +1368,39 @@
         <v>10</v>
       </c>
       <c r="E1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J1" t="s">
+        <v>49</v>
+      </c>
+      <c r="K1" t="s">
         <v>50</v>
       </c>
-      <c r="K1" t="s">
-        <v>51</v>
-      </c>
       <c r="L1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="M1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="N1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C2" t="s">
         <v>15</v>
@@ -1421,129 +1409,129 @@
         <v>24</v>
       </c>
       <c r="E2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J2" t="s">
+        <v>61</v>
+      </c>
+      <c r="K2" t="s">
         <v>62</v>
       </c>
-      <c r="K2" t="s">
-        <v>63</v>
-      </c>
       <c r="L2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D3" t="s">
         <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="L3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D4" t="s">
         <v>17</v>
       </c>
       <c r="E4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="M4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="N4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D5" t="s">
         <v>18</v>
       </c>
       <c r="E5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="M5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="N5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D6" t="s">
         <v>19</v>
       </c>
       <c r="E6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
@@ -1551,10 +1539,10 @@
         <v>20</v>
       </c>
       <c r="F7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
@@ -1562,7 +1550,7 @@
         <v>21</v>
       </c>
       <c r="M8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
@@ -1570,7 +1558,7 @@
         <v>22</v>
       </c>
       <c r="M9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
@@ -1578,132 +1566,132 @@
         <v>23</v>
       </c>
       <c r="M10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="M11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="M12" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="M13" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="M14" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="18" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M18" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="19" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M19" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="20" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M20" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="21" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M21" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="22" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M22" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="23" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M23" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="24" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M24" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="25" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M25" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="26" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M26" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M27" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="28" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M28" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="29" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M29" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="30" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M30" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="31" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M31" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="32" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M32" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="33" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M33" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="34" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="35" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M35" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>
